--- a/docs/demo/07_PDI_register_demo.xlsx
+++ b/docs/demo/07_PDI_register_demo.xlsx
@@ -117,7 +117,7 @@
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">02/02/2024</t>
+          <t xml:space="preserve">18/02/2021</t>
         </is>
       </c>
       <c r="D2" t="inlineStr" s="2">
@@ -137,7 +137,7 @@
       </c>
       <c r="G2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2024-0001</t>
+          <t xml:space="preserve">PDI-2021-0001</t>
         </is>
       </c>
     </row>
@@ -154,7 +154,7 @@
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">02/02/2024</t>
+          <t xml:space="preserve">18/02/2021</t>
         </is>
       </c>
       <c r="D3" t="inlineStr" s="2">
@@ -174,7 +174,7 @@
       </c>
       <c r="G3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2024-0001</t>
+          <t xml:space="preserve">PDI-2021-0001</t>
         </is>
       </c>
     </row>
@@ -191,7 +191,7 @@
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">03/03/2025</t>
+          <t xml:space="preserve">27/08/2021</t>
         </is>
       </c>
       <c r="D4" t="inlineStr" s="2">
@@ -211,7 +211,7 @@
       </c>
       <c r="G4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2025-0002</t>
+          <t xml:space="preserve">PDI-2021-0002</t>
         </is>
       </c>
     </row>
@@ -228,7 +228,7 @@
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">03/03/2025</t>
+          <t xml:space="preserve">27/08/2021</t>
         </is>
       </c>
       <c r="D5" t="inlineStr" s="2">
@@ -248,7 +248,7 @@
       </c>
       <c r="G5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2025-0002</t>
+          <t xml:space="preserve">PDI-2021-0002</t>
         </is>
       </c>
     </row>
@@ -265,7 +265,7 @@
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04/04/2023</t>
+          <t xml:space="preserve">17/06/2020</t>
         </is>
       </c>
       <c r="D6" t="inlineStr" s="2">
@@ -285,7 +285,7 @@
       </c>
       <c r="G6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2023-0003</t>
+          <t xml:space="preserve">PDI-2020-0003</t>
         </is>
       </c>
     </row>
@@ -302,7 +302,7 @@
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04/04/2023</t>
+          <t xml:space="preserve">17/06/2020</t>
         </is>
       </c>
       <c r="D7" t="inlineStr" s="2">
@@ -322,7 +322,7 @@
       </c>
       <c r="G7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2023-0003</t>
+          <t xml:space="preserve">PDI-2020-0003</t>
         </is>
       </c>
     </row>
@@ -339,7 +339,7 @@
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">05/05/2024</t>
+          <t xml:space="preserve">24/11/2019</t>
         </is>
       </c>
       <c r="D8" t="inlineStr" s="2">
@@ -359,7 +359,7 @@
       </c>
       <c r="G8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2024-0004</t>
+          <t xml:space="preserve">PDI-2019-0004</t>
         </is>
       </c>
     </row>
@@ -376,7 +376,7 @@
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">05/05/2024</t>
+          <t xml:space="preserve">24/11/2019</t>
         </is>
       </c>
       <c r="D9" t="inlineStr" s="2">
@@ -396,7 +396,7 @@
       </c>
       <c r="G9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2024-0004</t>
+          <t xml:space="preserve">PDI-2019-0004</t>
         </is>
       </c>
     </row>
@@ -413,7 +413,7 @@
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06/06/2025</t>
+          <t xml:space="preserve">05/07/2020</t>
         </is>
       </c>
       <c r="D10" t="inlineStr" s="2">
@@ -433,7 +433,7 @@
       </c>
       <c r="G10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2025-0005</t>
+          <t xml:space="preserve">PDI-2020-0005</t>
         </is>
       </c>
     </row>
@@ -450,7 +450,7 @@
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06/06/2025</t>
+          <t xml:space="preserve">05/07/2020</t>
         </is>
       </c>
       <c r="D11" t="inlineStr" s="2">
@@ -470,7 +470,7 @@
       </c>
       <c r="G11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2025-0005</t>
+          <t xml:space="preserve">PDI-2020-0005</t>
         </is>
       </c>
     </row>
@@ -487,7 +487,7 @@
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07/07/2023</t>
+          <t xml:space="preserve">05/10/2021</t>
         </is>
       </c>
       <c r="D12" t="inlineStr" s="2">
@@ -507,7 +507,7 @@
       </c>
       <c r="G12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2023-0006</t>
+          <t xml:space="preserve">PDI-2021-0006</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07/07/2023</t>
+          <t xml:space="preserve">05/10/2021</t>
         </is>
       </c>
       <c r="D13" t="inlineStr" s="2">
@@ -544,7 +544,7 @@
       </c>
       <c r="G13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2023-0006</t>
+          <t xml:space="preserve">PDI-2021-0006</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08/08/2024</t>
+          <t xml:space="preserve">10/09/2020</t>
         </is>
       </c>
       <c r="D14" t="inlineStr" s="2">
@@ -581,7 +581,7 @@
       </c>
       <c r="G14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2024-0007</t>
+          <t xml:space="preserve">PDI-2020-0007</t>
         </is>
       </c>
     </row>
@@ -598,7 +598,7 @@
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08/08/2024</t>
+          <t xml:space="preserve">10/09/2020</t>
         </is>
       </c>
       <c r="D15" t="inlineStr" s="2">
@@ -618,7 +618,7 @@
       </c>
       <c r="G15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2024-0007</t>
+          <t xml:space="preserve">PDI-2020-0007</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09/09/2025</t>
+          <t xml:space="preserve">16/02/2020</t>
         </is>
       </c>
       <c r="D16" t="inlineStr" s="2">
@@ -655,7 +655,7 @@
       </c>
       <c r="G16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2025-0008</t>
+          <t xml:space="preserve">PDI-2020-0008</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09/09/2025</t>
+          <t xml:space="preserve">16/02/2020</t>
         </is>
       </c>
       <c r="D17" t="inlineStr" s="2">
@@ -692,7 +692,7 @@
       </c>
       <c r="G17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2025-0008</t>
+          <t xml:space="preserve">PDI-2020-0008</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,7 @@
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10/10/2023</t>
+          <t xml:space="preserve">18/05/2021</t>
         </is>
       </c>
       <c r="D18" t="inlineStr" s="2">
@@ -729,7 +729,7 @@
       </c>
       <c r="G18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2023-0009</t>
+          <t xml:space="preserve">PDI-2021-0009</t>
         </is>
       </c>
       <c r="H18" t="inlineStr" s="2">
@@ -751,7 +751,7 @@
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">10/10/2023</t>
+          <t xml:space="preserve">18/05/2021</t>
         </is>
       </c>
       <c r="D19" t="inlineStr" s="2">
@@ -771,7 +771,7 @@
       </c>
       <c r="G19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2023-0009</t>
+          <t xml:space="preserve">PDI-2021-0009</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11/11/2024</t>
+          <t xml:space="preserve">13/05/2023</t>
         </is>
       </c>
       <c r="D20" t="inlineStr" s="2">
@@ -808,7 +808,7 @@
       </c>
       <c r="G20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2024-0010</t>
+          <t xml:space="preserve">PDI-2023-0010</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11/11/2024</t>
+          <t xml:space="preserve">13/05/2023</t>
         </is>
       </c>
       <c r="D21" t="inlineStr" s="2">
@@ -845,7 +845,7 @@
       </c>
       <c r="G21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2024-0010</t>
+          <t xml:space="preserve">PDI-2023-0010</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12/12/2025</t>
+          <t xml:space="preserve">09/06/2021</t>
         </is>
       </c>
       <c r="D22" t="inlineStr" s="2">
@@ -882,7 +882,7 @@
       </c>
       <c r="G22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2025-0011</t>
+          <t xml:space="preserve">PDI-2021-0011</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12/12/2025</t>
+          <t xml:space="preserve">09/06/2021</t>
         </is>
       </c>
       <c r="D23" t="inlineStr" s="2">
@@ -919,7 +919,7 @@
       </c>
       <c r="G23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2025-0011</t>
+          <t xml:space="preserve">PDI-2021-0011</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13/01/2023</t>
+          <t xml:space="preserve">26/03/2020</t>
         </is>
       </c>
       <c r="D24" t="inlineStr" s="2">
@@ -956,7 +956,7 @@
       </c>
       <c r="G24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2023-0012</t>
+          <t xml:space="preserve">PDI-2020-0012</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13/01/2023</t>
+          <t xml:space="preserve">26/03/2020</t>
         </is>
       </c>
       <c r="D25" t="inlineStr" s="2">
@@ -993,7 +993,7 @@
       </c>
       <c r="G25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2023-0012</t>
+          <t xml:space="preserve">PDI-2020-0012</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14/02/2024</t>
+          <t xml:space="preserve">05/09/2020</t>
         </is>
       </c>
       <c r="D26" t="inlineStr" s="2">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="G26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2024-0013</t>
+          <t xml:space="preserve">PDI-2020-0013</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14/02/2024</t>
+          <t xml:space="preserve">05/09/2020</t>
         </is>
       </c>
       <c r="D27" t="inlineStr" s="2">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="G27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2024-0013</t>
+          <t xml:space="preserve">PDI-2020-0013</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">15/03/2025</t>
+          <t xml:space="preserve">01/06/2020</t>
         </is>
       </c>
       <c r="D28" t="inlineStr" s="2">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="G28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2025-0014</t>
+          <t xml:space="preserve">PDI-2020-0014</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">15/03/2025</t>
+          <t xml:space="preserve">01/06/2020</t>
         </is>
       </c>
       <c r="D29" t="inlineStr" s="2">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="G29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2025-0014</t>
+          <t xml:space="preserve">PDI-2020-0014</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">16/04/2023</t>
+          <t xml:space="preserve">02/09/2021</t>
         </is>
       </c>
       <c r="D30" t="inlineStr" s="2">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="G30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2023-0015</t>
+          <t xml:space="preserve">PDI-2021-0015</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">16/04/2023</t>
+          <t xml:space="preserve">02/09/2021</t>
         </is>
       </c>
       <c r="D31" t="inlineStr" s="2">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2023-0015</t>
+          <t xml:space="preserve">PDI-2021-0015</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">17/05/2024</t>
+          <t xml:space="preserve">03/11/2021</t>
         </is>
       </c>
       <c r="D32" t="inlineStr" s="2">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="G32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2024-0016</t>
+          <t xml:space="preserve">PDI-2021-0016</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">17/05/2024</t>
+          <t xml:space="preserve">03/11/2021</t>
         </is>
       </c>
       <c r="D33" t="inlineStr" s="2">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="G33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2024-0016</t>
+          <t xml:space="preserve">PDI-2021-0016</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18/06/2025</t>
+          <t xml:space="preserve">30/11/2019</t>
         </is>
       </c>
       <c r="D34" t="inlineStr" s="2">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="G34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2025-0017</t>
+          <t xml:space="preserve">PDI-2019-0017</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18/06/2025</t>
+          <t xml:space="preserve">30/11/2019</t>
         </is>
       </c>
       <c r="D35" t="inlineStr" s="2">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="G35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2025-0017</t>
+          <t xml:space="preserve">PDI-2019-0017</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19/07/2023</t>
+          <t xml:space="preserve">28/02/2021</t>
         </is>
       </c>
       <c r="D36" t="inlineStr" s="2">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="G36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2023-0018</t>
+          <t xml:space="preserve">PDI-2021-0018</t>
         </is>
       </c>
       <c r="H36" t="inlineStr" s="2">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19/07/2023</t>
+          <t xml:space="preserve">28/02/2021</t>
         </is>
       </c>
       <c r="D37" t="inlineStr" s="2">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="G37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2023-0018</t>
+          <t xml:space="preserve">PDI-2021-0018</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">20/08/2024</t>
+          <t xml:space="preserve">20/12/2019</t>
         </is>
       </c>
       <c r="D38" t="inlineStr" s="2">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="G38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2024-0019</t>
+          <t xml:space="preserve">PDI-2019-0019</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">20/08/2024</t>
+          <t xml:space="preserve">20/12/2019</t>
         </is>
       </c>
       <c r="D39" t="inlineStr" s="2">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="G39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2024-0019</t>
+          <t xml:space="preserve">PDI-2019-0019</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">21/09/2025</t>
+          <t xml:space="preserve">03/05/2021</t>
         </is>
       </c>
       <c r="D40" t="inlineStr" s="2">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="G40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2025-0020</t>
+          <t xml:space="preserve">PDI-2021-0020</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">21/09/2025</t>
+          <t xml:space="preserve">03/05/2021</t>
         </is>
       </c>
       <c r="D41" t="inlineStr" s="2">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="G41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2025-0020</t>
+          <t xml:space="preserve">PDI-2021-0020</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">22/10/2023</t>
+          <t xml:space="preserve">22/02/2020</t>
         </is>
       </c>
       <c r="D42" t="inlineStr" s="2">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="G42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2023-0021</t>
+          <t xml:space="preserve">PDI-2020-0021</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">22/10/2023</t>
+          <t xml:space="preserve">22/02/2020</t>
         </is>
       </c>
       <c r="D43" t="inlineStr" s="2">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="G43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2023-0021</t>
+          <t xml:space="preserve">PDI-2020-0021</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">23/11/2024</t>
+          <t xml:space="preserve">30/08/2020</t>
         </is>
       </c>
       <c r="D44" t="inlineStr" s="2">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="G44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2024-0022</t>
+          <t xml:space="preserve">PDI-2020-0022</t>
         </is>
       </c>
     </row>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">23/11/2024</t>
+          <t xml:space="preserve">30/08/2020</t>
         </is>
       </c>
       <c r="D45" t="inlineStr" s="2">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="G45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2024-0022</t>
+          <t xml:space="preserve">PDI-2020-0022</t>
         </is>
       </c>
     </row>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">24/12/2025</t>
+          <t xml:space="preserve">04/11/2020</t>
         </is>
       </c>
       <c r="D46" t="inlineStr" s="2">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="G46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2025-0023</t>
+          <t xml:space="preserve">PDI-2020-0023</t>
         </is>
       </c>
     </row>
@@ -1792,7 +1792,7 @@
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">24/12/2025</t>
+          <t xml:space="preserve">04/11/2020</t>
         </is>
       </c>
       <c r="D47" t="inlineStr" s="2">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="G47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2025-0023</t>
+          <t xml:space="preserve">PDI-2020-0023</t>
         </is>
       </c>
     </row>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">25/01/2023</t>
+          <t xml:space="preserve">21/08/2020</t>
         </is>
       </c>
       <c r="D48" t="inlineStr" s="2">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="G48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2023-0024</t>
+          <t xml:space="preserve">PDI-2020-0024</t>
         </is>
       </c>
     </row>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">25/01/2023</t>
+          <t xml:space="preserve">21/08/2020</t>
         </is>
       </c>
       <c r="D49" t="inlineStr" s="2">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="G49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2023-0024</t>
+          <t xml:space="preserve">PDI-2020-0024</t>
         </is>
       </c>
     </row>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">26/02/2024</t>
+          <t xml:space="preserve">26/01/2024</t>
         </is>
       </c>
       <c r="D50" t="inlineStr" s="2">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">26/02/2024</t>
+          <t xml:space="preserve">26/01/2024</t>
         </is>
       </c>
       <c r="D51" t="inlineStr" s="2">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">27/03/2025</t>
+          <t xml:space="preserve">11/09/2020</t>
         </is>
       </c>
       <c r="D52" t="inlineStr" s="2">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="G52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2025-0026</t>
+          <t xml:space="preserve">PDI-2020-0026</t>
         </is>
       </c>
     </row>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">27/03/2025</t>
+          <t xml:space="preserve">11/09/2020</t>
         </is>
       </c>
       <c r="D53" t="inlineStr" s="2">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="G53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2025-0026</t>
+          <t xml:space="preserve">PDI-2020-0026</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">01/04/2023</t>
+          <t xml:space="preserve">26/01/2021</t>
         </is>
       </c>
       <c r="D54" t="inlineStr" s="2">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2023-0027</t>
+          <t xml:space="preserve">PDI-2021-0027</t>
         </is>
       </c>
       <c r="H54" t="inlineStr" s="2">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">01/04/2023</t>
+          <t xml:space="preserve">26/01/2021</t>
         </is>
       </c>
       <c r="D55" t="inlineStr" s="2">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="G55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2023-0027</t>
+          <t xml:space="preserve">PDI-2021-0027</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">02/05/2024</t>
+          <t xml:space="preserve">14/11/2019</t>
         </is>
       </c>
       <c r="D56" t="inlineStr" s="2">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="G56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2024-0028</t>
+          <t xml:space="preserve">PDI-2019-0028</t>
         </is>
       </c>
     </row>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">02/05/2024</t>
+          <t xml:space="preserve">14/11/2019</t>
         </is>
       </c>
       <c r="D57" t="inlineStr" s="2">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="G57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2024-0028</t>
+          <t xml:space="preserve">PDI-2019-0028</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">03/06/2025</t>
+          <t xml:space="preserve">21/05/2020</t>
         </is>
       </c>
       <c r="D58" t="inlineStr" s="2">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="G58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2025-0029</t>
+          <t xml:space="preserve">PDI-2020-0029</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">03/06/2025</t>
+          <t xml:space="preserve">21/05/2020</t>
         </is>
       </c>
       <c r="D59" t="inlineStr" s="2">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="G59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2025-0029</t>
+          <t xml:space="preserve">PDI-2020-0029</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04/07/2023</t>
+          <t xml:space="preserve">16/05/2022</t>
         </is>
       </c>
       <c r="D60" t="inlineStr" s="2">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="G60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2023-0030</t>
+          <t xml:space="preserve">PDI-2022-0030</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">04/07/2023</t>
+          <t xml:space="preserve">16/05/2022</t>
         </is>
       </c>
       <c r="D61" t="inlineStr" s="2">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="G61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PDI-2023-0030</t>
+          <t xml:space="preserve">PDI-2022-0030</t>
         </is>
       </c>
     </row>
